--- a/output/2026-10-02_21_Malesia_Negeri_Sembilan_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-02_21_Malesia_Negeri_Sembilan_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-10-02_21_Malesia_Negeri_Sembilan_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-02_21_Malesia_Negeri_Sembilan_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Azienda reale verificata tramite fetch diretto del sito ufficiale: Lapasar Sdn Bhd, Company No. 1198228-D, registrata Ministry of Finance. Sede legale a Klang, Selangor (NON in Negeri Sembilan), ma marketplace/distributore B2B strutturato che serve attivamente l'area di Seremban/Senawang/Nilai con logistica propria e catalogo di 10.000+ fornitori per l'industria locale. Da valutare umanamente se considerarlo "distributore nella zona" in senso stretto o solo canale di vendita regionale esterno.</t>
+          <t>Azienda reale verificata tramite fetch diretto del sito ufficiale: Lapasar Sdn Bhd, Company No. 1198228-D, registrata Ministry of Finance. Sede legale a Klang, Selangor (NON in Negeri Sembilan), ma marketplace/distributore B2B strutturato che serve attivamente l'area di Seremban/Senawang/Nilai con logistica propria e catalogo di 10.000+ fornitori per l'industria locale. Da valutare umanamente se considerarlo "distributore nella zona" in senso stretto o solo canale di vendita regionale esterno. [DUPLICATO — vedi anche: 2026-10-02_19_Malesia_Negeri_Sembilan_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
